--- a/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PASS 680 · WARN 22 · ERROR 0 · SKIP 0</t>
+          <t>PASS 695 · WARN 23 · ERROR 0 · SKIP 0</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/11 테이블에 행 있음</t>
+          <t>5/11 테이블에 행 있음</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>실행 흔적 3회 · 점수 미수집</t>
+          <t>실행 흔적 0회 · 점수 미수집</t>
         </is>
       </c>
     </row>
@@ -543,13 +543,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01c7ce6c-0208-e79d-0005-852e00057a6a</t>
+          <t>01c7dba5-0208-f4ea-0005-869e0007cf72</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 23:04:54.331000-07:00</t>
+          <t>2026-10-20 07:29:00.229000-07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-17 23:05:09.117000-07:00</t>
+          <t>2026-10-20 07:29:20.659000-07:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -622,17 +622,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01c7ce6d-0208-e110-0005-852e0005844e</t>
+          <t>01c7dba5-0208-f4e9-0005-869e00080172</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17 23:05:09.137000-07:00</t>
+          <t>2026-10-20 07:29:20.730000-07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-17 23:05:35.799000-07:00</t>
+          <t>2026-10-20 07:29:44.811000-07:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -651,17 +651,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01c7ce6d-0208-e110-0005-852e00058692</t>
+          <t>01c7dba5-0208-f7f4-0005-869e0008117a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 23:05:36.150000-07:00</t>
+          <t>2026-10-20 07:29:44.972000-07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-17 23:15:45.657000-07:00</t>
+          <t>2026-10-20 07:40:35.863000-07:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -680,17 +680,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01c7ce77-0208-e79d-0005-852e00065df6</t>
+          <t>01c7dbb0-0208-f7f4-0005-869e0008d992</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-17 23:15:45.806000-07:00</t>
+          <t>2026-10-20 07:40:35.922000-07:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-17 23:18:03.908000-07:00</t>
+          <t>2026-10-20 07:43:06.595000-07:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01c7d010-0208-e110-0005-852e000e7d72</t>
+          <t>01c7dd59-0208-f4ee-0005-869e000cc03a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 06:04:52.472000-07:00</t>
+          <t>2026-10-20 14:45:09.525000-07:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-18 06:05:26.885000-07:00</t>
+          <t>2026-10-20 14:45:30.419000-07:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>--select FACT_AD_PERFORMANCE+ FACT_BUDGET FACT_BUDGET_YEARLY</t>
+          <t>--select FACT_MEMBER_COHORT_SURVIVAL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -742,39 +742,6 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>01c7d4f1-0208-eda9-0005-852e00156666</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-19 02:53:08.629000-07:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-10-19 02:53:44.687000-07:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>--select FACT_AD_PERFORMANCE+ FACT_BUDGET FACT_BUDGET_YEARLY</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -787,13 +754,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -817,7 +784,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Done. PASS=680 WARN=22 ERROR=0 SKIP=0 TOTAL=702</t>
+          <t>Done. PASS=695 WARN=23 ERROR=0 SKIP=0 TOTAL=718</t>
         </is>
       </c>
     </row>
@@ -961,7 +928,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_PATH_NM</t>
         </is>
       </c>
     </row>
@@ -973,7 +940,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_PATH_NM</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
         </is>
       </c>
     </row>
@@ -1082,6 +1049,18 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>Warning in test relationships_FACT_MEMBER_MONTHLY_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Warning in test warn_gold_view_comment_coverage</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1081,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1115,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-17 23:07:56.269000-07:00</t>
+          <t>2026-10-20 07:32:19.186000-07:00</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1132,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-17 23:07:56.329000-07:00</t>
+          <t>2026-10-20 07:32:19.166000-07:00</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1149,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-17 23:07:56.329000-07:00</t>
+          <t>2026-10-20 07:32:19.420000-07:00</t>
         </is>
       </c>
     </row>
@@ -1187,31 +1166,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-17 23:08:35.113000-07:00</t>
+          <t>2026-10-20 07:33:00.884000-07:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WARN_BIGQUERY_LOAD_GAP</t>
+          <t>WARN_GOLD_VIEW_COMMENT_COVERAGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-17 23:17:13.877000-07:00</t>
+          <t>2026-10-20 07:42:58.460000-07:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID</t>
+          <t>WARN_BIGQUERY_LOAD_GAP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1221,14 +1200,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-17 23:06:18.975000-07:00</t>
+          <t>2026-10-20 07:42:07.385000-07:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID_ROWS</t>
+          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1238,14 +1217,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-17 23:06:19.073000-07:00</t>
+          <t>2026-10-20 07:30:32.532000-07:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WARN_FMM_FUTURE_MONTH_CAP</t>
+          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID_ROWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1255,14 +1234,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-17 23:13:45.423000-07:00</t>
+          <t>2026-10-20 07:30:32.751000-07:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WARN_GOLD_FACT_BIGQUERY_DATE_SK_ZERO</t>
+          <t>WARN_FMM_FUTURE_MONTH_CAP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1272,14 +1251,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-17 23:17:53.745000-07:00</t>
+          <t>2026-10-20 07:38:14.768000-07:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WARN_GOLD_VIEW_COMMENT_COVERAGE</t>
+          <t>WARN_GOLD_FACT_BIGQUERY_DATE_SK_ZERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1289,7 +1268,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-19 02:53:39.415000-07:00</t>
+          <t>2026-10-20 07:42:51.872000-07:00</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1285,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-17 23:06:20.662000-07:00</t>
+          <t>2026-10-20 07:30:33.915000-07:00</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1306,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1535,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1660,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1581079.0</t>
+          <t>1582092.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-4844.0</t>
+          <t>-3831.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1708,12 +1687,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>933151.0</t>
+          <t>933717.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30087.0</t>
+          <t>30653.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1735,12 +1714,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>946950002274.0</t>
+          <t>946965530131.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51771693166.0</t>
+          <t>51787221023.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1762,12 +1741,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>956555915668.0</t>
+          <t>960986496575.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>64596124780.0</t>
+          <t>69026705687.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1924,12 +1903,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4059502.2214</t>
+          <t>4062074.4714</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1767624.2214000002</t>
+          <t>1770196.4714000002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1951,12 +1930,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1076058.0</t>
+          <t>1076739.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37796.0</t>
+          <t>38477.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1978,12 +1957,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1001042.0</t>
+          <t>1003161.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-133084.0</t>
+          <t>-130965.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2005,12 +1984,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>319473.0</t>
+          <t>319900.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-87750.0</t>
+          <t>-87323.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2059,12 +2038,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>44406102.0</t>
+          <t>44490520.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5935322.0</t>
+          <t>6019740.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2086,12 +2065,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1063801.0</t>
+          <t>1064999.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31830.0</t>
+          <t>33028.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2144,7 +2123,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2283,13 +2262,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py IW20760 · 2026-10-20 13:12 KST · 입력 = _ENV/IW20760/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2317,87 +2296,6 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>LAST_T</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>E3FCEC7884324C41A1256405825971C7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:53.317000-07:00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:16:10.568000-07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>0DDAA7B8C0E24F3C8D1F2AA7E0351B0F</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:10:02.578000-07:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:19:00.066000-07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5B1978E8F3B84CD1B7A40F454BECCEBA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:10:11.607000-07:00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:15:12.668000-07:00</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PASS 695 · WARN 23 · ERROR 0 · SKIP 0</t>
+          <t>PASS 678 · WARN 24 · ERROR 0 · SKIP 0</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5/11 테이블에 행 있음</t>
+          <t>5/12 테이블에 행 있음</t>
         </is>
       </c>
     </row>
@@ -543,13 +543,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -593,25 +593,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01c7dba5-0208-f4ea-0005-869e0007cf72</t>
+          <t>01c7b830-0002-2ae9-0001-72de0563c3a2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 07:29:00.229000-07:00</t>
+          <t>2026-10-14 16:12:17.019000+09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-20 07:29:20.659000-07:00</t>
+          <t>2026-10-14 16:12:36.666000+09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>--select AGENCY_AD_ROW_DGT+</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -622,46 +626,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01c7dba5-0208-f4e9-0005-869e00080172</t>
+          <t>01c7b830-0002-2ae9-0001-72de0563c4fa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 07:29:20.730000-07:00</t>
+          <t>2026-10-14 16:12:43.108000+09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-20 07:29:44.811000-07:00</t>
+          <t>2026-10-14 16:12:43.356000+09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>compile</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>--select AGENCY_AD_ROW_DGT+</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No active warehouse selected in the current session.  Select an active warehouse with the 'use warehouse' command. ⏎ </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01c7dba5-0208-f7f4-0005-869e0008117a</t>
+          <t>01c7b830-0002-2984-0001-72de0563f062</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 07:29:44.972000-07:00</t>
+          <t>2026-10-14 16:12:53.485000+09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-20 07:40:35.863000-07:00</t>
+          <t>2026-10-14 16:13:41.767000+09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -669,7 +681,11 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>--select AGENCY_AD_ROW_DGT+</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -680,17 +696,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01c7dbb0-0208-f7f4-0005-869e0008d992</t>
+          <t>01c7b836-0002-2984-0001-72de05645a6a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 07:40:35.922000-07:00</t>
+          <t>2026-10-14 16:18:51.261000+09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-20 07:43:06.595000-07:00</t>
+          <t>2026-10-14 16:19:37.364000+09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -700,7 +716,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
+          <t>--select AGENCY_AD_ROW_DGT+ AGENCY_AD_CREATIVE+ AGENCY_AD_PERFORMANCE+ AGENCY_AD_DIGITAL+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -713,17 +729,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01c7dd59-0208-f4ee-0005-869e000cc03a</t>
+          <t>01c7bb6d-0002-2c93-0001-72de058b884e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 14:45:09.525000-07:00</t>
+          <t>2026-10-15 06:01:01.813000+09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-20 14:45:30.419000-07:00</t>
+          <t>2026-10-15 06:10:56.123000+09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -731,17 +747,1452 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>--select FACT_MEMBER_COHORT_SURVIVAL</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>01c7bba3-0002-2d5f-0001-72de058e7416</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:55:56.049000+09:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:56:13.673000+09:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>01c7bba4-0002-2ae9-0001-72de058e56aa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:56:14.799000+09:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:56:36.646000+09:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>01c7bba4-0002-2d5f-0001-72de058e76c2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:56:38.242000+09:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:05:46.848000+09:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>01c7bbae-0002-2cbb-0001-72de058f3772</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:06:36.526000+09:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:10:16.760000+09:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01c7bc66-0002-2d8a-0001-72de0598c9f2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:10:13.618000+09:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:10:37.658000+09:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>--select DIM_MARKETING_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>01c7bce8-0002-2d5f-0001-72de05a015de</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:20:54.911000+09:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:24:42.395000+09:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DBT job failed: 4 model(s) failed out of 656 total (total time: 206.62s) ⏎ First error in model 'CRM_SEND_MEMBER': Database Error in model CRM_SEND_MEMBER (models/silver/crm/CRM_SEND_MEMBER.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'CRM_SEND_MEMBER'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.SILVER.CRM_SEND_MEMBER. ⏎ Error 2 in model 'DIM_CAMPAIGN': Database Error in model DIM_CAMPAIGN (models/gold/dim/DIM_CAMPAIGN.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'DIM_CAMPAIGN'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.GOLD.DIM_CAMPAIGN. ⏎ Error 3 in model 'FACT_EXPENSE_RESOLUTION': Database Error in model FACT_EXPENSE_RESOLUTION (models/gold/fact/FACT_EXPENSE_RESOLUTION.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'FACT_EXPENSE_RESOLUTION'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.GOLD.FACT_EXPENSE_RESOLUTION. ⏎ Error 4 in model 'FACT_AD_PERFORMANCE': Database Error in model FACT_AD_PERFORMANCE (models/gold/fact/FACT_AD_PERFORMANCE.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'FACT_AD_PERFORMANCE'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.GOLD.FACT_AD_PERFORMANCE..  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7bce8-0002-2d5f-0001-72de05a015de') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>01c7bcfb-0002-2d5f-0001-72de05a14056</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:39:51.192000+09:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:40:21.176000+09:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>retry</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎ [0m03:40:19    Got 271489 results, configured to fail if != 0 ⏎ [0m03:40:19   ⏎ [0m03:40:19    compiled code at target/compiled/gn_dw_silver/models/gold/_gold_ready_schema.yml/relationships_FACT_AD_PERFORMA_113fefc940e6a2beee03c97acac8ee59.sql ⏎ [0m03:40:19   ⏎ [0m03:40:20  [33mWarning in test warn_fap_mktg_unmapped_ratio (tests/warn_fap_mktg_unmapped_ratio.sql)[0m ⏎ [0m03:40:20  Got 1 result, configured to warn if != 0 ⏎ [0m03:40:20   ⏎ [0m03:40:20    compiled code at target/compiled/gn_dw_silver/tests/warn_fap_mktg_unmapped_ratio.sql ⏎ [0m03:40:20   ⏎ [0m03:40:20  Done. PASS=32 WARN=1 ERROR=7 SKIP=78 TOTAL=118. ⏎  Run select system$get_dbt_log('01c7bcfb-0002-2d5f-0001-72de05a14056') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>01c7bcff-0002-2d6f-0001-72de05a14002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:43:58.942000+09:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:54:02.042000+09:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 656 total (total time: 576.62s) ⏎ First error in model 'CRM_SEND_MEMBER': Database Error in model CRM_SEND_MEMBER (models/silver/crm/CRM_SEND_MEMBER.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'CRM_SEND_MEMBER'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.SILVER.CRM_SEND_MEMBER..  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7bcff-0002-2d6f-0001-72de05a14002') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>01c7bd29-0002-2d8a-0001-72de05a3afd2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:25:27.299000+09:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:36:50.025000+09:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>01c7c07d-0002-2f20-0001-72de05d186e6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:37:48.576000+09:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:38:10.317000+09:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>01c7c07e-0002-2f1f-0001-72de05d16986</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:38:14.183000+09:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:38:37.133000+09:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>01c7c07e-0002-2f16-0001-72de05d198f6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:38:38.072000+09:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:51:04.487000+09:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>01c7c09f-0002-2f1f-0001-72de05d40046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:11:06.158000+09:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:11:37.208000+09:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>--select FACT_AD_PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎ [0m19:11:35    Got 271489 results, configured to fail if != 0 ⏎ [0m19:11:35   ⏎ [0m19:11:35    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/models/gold/_gold_ready_schema.yml/relationships_FACT_AD_PERFORMA_113fefc940e6a2beee03c97acac8ee59.sql ⏎ [0m19:11:35   ⏎ [0m19:11:35  [33mWarning in test warn_fap_mktg_unmapped_ratio (tests/warn_fap_mktg_unmapped_ratio.sql)[0m ⏎ [0m19:11:35  Got 1 result, configured to warn if != 0 ⏎ [0m19:11:35   ⏎ [0m19:11:35    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fap_mktg_unmapped_ratio.sql ⏎ [0m19:11:35   ⏎ [0m19:11:35  Done. PASS=15 WARN=1 ERROR=4 SKIP=0 TOTAL=20. ⏎  Run select system$get_dbt_log('01c7c09f-0002-2f1f-0001-72de05d40046') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>01c7c0a0-0002-2f1f-0001-72de05d4057a</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:12:01.280000+09:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:12:54.537000+09:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>--select +FACT_AD_PERFORMANCE+</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎   ---------------------------------------------- ⏎   select * from GN_DW.OPS.warn_bigquery_load_gap ⏎   ---------------------------------------------- ⏎ [0m19:12:51   ⏎ [0m19:12:51  [33mWarning in test warn_fer_mktg_campaign_multi (tests/warn_fer_mktg_campaign_multi.sql)[0m ⏎ [0m19:12:51  Got 1 result, configured to warn if != 0 ⏎ [0m19:12:51   ⏎ [0m19:12:51    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fer_mktg_campaign_multi.sql ⏎ [0m19:12:51   ⏎ [0m19:12:51  Done. PASS=89 WARN=5 ERROR=2 SKIP=5 TOTAL=101. ⏎  Run select system$get_dbt_log('01c7c0a0-0002-2f1f-0001-72de05d4057a') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>01c7c0a1-0002-2f1f-0001-72de05d4354e</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:13:19.052000+09:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:13:31.999000+09:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>01c7c0a1-0002-2f1f-0001-72de05d43636</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:13:34.397000+09:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:13:56.204000+09:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>01c7c0a2-0002-2f20-0001-72de05d443b2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:03.543000+09:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:25:38.673000+09:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>01c7c0bb-0002-2f16-0001-72de05d5f79a</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:39:47.441000+09:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:07.752000+09:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>01c7c0bc-0002-2f20-0001-72de05d5eef6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:14.586000+09:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:40:17.700000+09:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>01c7c0be-0002-2f20-0001-72de05d628ae</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:42:13.273000+09:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:42:31.219000+09:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>01c7c0be-0002-2f1f-0001-72de05d61fb2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:42:32.900000+09:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:42:54.690000+09:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>01c7c0be-0002-2f20-0001-72de05d62c72</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:42:56.364000+09:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:34.343000+09:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>01c7c10d-0002-2f1f-0001-72de05dae2a2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01:00.683000+09:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:12:44.758000+09:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>01c7c399-0002-2f1f-0001-72de0600c2aa</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:53:37.341000+09:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:19:33.229000+09:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎   --------------------------------------------------------------------------------------- ⏎   select * from GN_DW.OPS.accepted_values_FACT_EVENT_ATT_a31e050516c23794739ccbd32aaa8c43 ⏎   --------------------------------------------------------------------------------------- ⏎ [0m08:19:21   ⏎ [0m08:19:21  [33mWarning in test warn_fmm_reason_unmapped_f_rows (tests/warn_fmm_reason_unmapped_f_rows.sql)[0m ⏎ [0m08:19:21  Got 1 result, configured to warn if != 0 ⏎ [0m08:19:21   ⏎ [0m08:19:21    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fmm_reason_unmapped_f_rows.sql ⏎ [0m08:19:21   ⏎ [0m08:19:21  Done. PASS=628 WARN=19 ERROR=8 SKIP=24 TOTAL=679. ⏎  Run select system$get_dbt_log('01c7c399-0002-2f1f-0001-72de0600c2aa') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>01c7c39a-0002-2f20-0001-72de0600b6de</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:54:02.224000+09:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:21:22.768000+09:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎   --------------------------------------------------------------------------------------- ⏎   select * from GN_DW.OPS.accepted_values_FACT_EVENT_ATT_a31e050516c23794739ccbd32aaa8c43 ⏎   --------------------------------------------------------------------------------------- ⏎ [0m08:21:09   ⏎ [0m08:21:09  [33mWarning in test warn_fmm_reason_unmapped_f_rows (tests/warn_fmm_reason_unmapped_f_rows.sql)[0m ⏎ [0m08:21:09  Got 1 result, configured to warn if != 0 ⏎ [0m08:21:09   ⏎ [0m08:21:09    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fmm_reason_unmapped_f_rows.sql ⏎ [0m08:21:09   ⏎ [0m08:21:09  Done. PASS=630 WARN=19 ERROR=6 SKIP=24 TOTAL=679. ⏎  Run select system$get_dbt_log('01c7c39a-0002-2f20-0001-72de0600b6de') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>01c7c3bb-0002-314b-0001-72de0603c88e</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:27:01.224000+09:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:27:18.931000+09:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>01c7c3bb-0002-30d2-0001-72de0603ab7a</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:27:19.974000+09:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:27:41.717000+09:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>01c7c3bb-0002-2f16-0001-72de0603ba66</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:27:42.453000+09:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:40:03.854000+09:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>01c7c4c7-0002-2f16-0001-72de0613769a</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:55:17.928000+09:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:55:36.347000+09:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>01c7c4c7-0002-2f16-0001-72de06137792</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:55:38.249000+09:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:55:59.819000+09:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>01c7c4c8-0002-2f1f-0001-72de061391f2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:56:01.399000+09:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:08:19.475000+09:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎ [0m13:08:08  Got 1 result, configured to warn if != 0 ⏎ [0m13:08:08   ⏎ [0m13:08:08    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fmm_reason_unmapped_f_rows.sql ⏎ [0m13:08:08   ⏎ [0m13:08:08  [33mWarning in test relationships_FACT_MEMBER_MONTHLY_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_ (models/gold/_gold_ready_schema.yml)[0m ⏎ [0m13:08:08  Got 181 results, configured to warn if != 0 ⏎ [0m13:08:08   ⏎ [0m13:08:08    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/models/gold/_gold_ready_schema.yml/relationships_FACT_MEMBER_MONT_53f1dbedc04314fed8831c443e382e05.sql ⏎ [0m13:08:08   ⏎ [0m13:08:08  Done. PASS=672 WARN=21 ERROR=1 SKIP=6 TOTAL=700. ⏎  Run select system$get_dbt_log('01c7c4c8-0002-2f1f-0001-72de061391f2') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>01c7c4ec-0002-30d2-0001-72de0616c5d6</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:32:45.118000+09:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:33:04.310000+09:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>01c7c4ed-0002-314b-0001-72de0616d25e</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:33:04.646000+09:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:33:26.918000+09:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>01c7c4ed-0002-2f20-0001-72de0616f126</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:33:27.921000+09:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:46:07.600000+09:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>01c7c6ad-0002-2f20-0001-72de0630252e</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01:00.819000+09:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:14:30.929000+09:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>01c7cc4d-0002-314d-0001-72de067a061a</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01:00.853000+09:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:13:53.565000+09:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>01c7d0bf-0002-32bf-0001-72de06abc732</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-19 00:59:46.644000+09:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00:05.432000+09:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>01c7d0c0-0002-3248-0001-72de06abbb46</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00:06.331000+09:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00:32.468000+09:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>01c7d0c0-0002-3248-0001-72de06abbe26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00:33.904000+09:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:13:30.483000+09:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>01c7d0cd-0002-3274-0001-72de06acd4fa</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:13:37.433000+09:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:23:21.095000+09:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>01c7d0d8-0002-3274-0001-72de06ad2e02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:24:21.420000+09:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-10-19 02:28:10.772000+09:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>01c7d1ed-0002-32bf-0001-72de06b76066</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01:00.817000+09:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:17:23.432000+09:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>01c7d78d-0002-35c4-0001-72de06e1f6c2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01:00.820000+09:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:17:20.799000+09:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>01c7dd2d-0002-365d-0001-72de071db1be</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01:00.616000+09:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:17:33.068000+09:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>01c7de96-0002-365d-0001-72de073035ce</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:02:45.704000+09:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:03:21.591000+09:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>--select FACT_MEMBER_COHORT_SURVIVAL DIM_SEND_REQUEST DIM_MSG_TEMPLATE DIM_MSG_TEMPLATE_BUTTON</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>01c7dea9-0002-365d-0001-72de07316e62</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:21:03.618000+09:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:22:03.139000+09:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>--select FACT_AD_INFLOW_ALLOC FACT_MEMBER_EVENT_COHORT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>01c7dec2-0002-365d-0001-72de07333032</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:46:00.189000+09:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:57:40.504000+09:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -754,13 +2205,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -784,7 +2235,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Done. PASS=695 WARN=23 ERROR=0 SKIP=0 TOTAL=718</t>
+          <t>Done. PASS=678 WARN=24 ERROR=0 SKIP=0 TOTAL=702</t>
         </is>
       </c>
     </row>
@@ -916,7 +2367,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warning in test warn_bigquery_load_gap</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
         </is>
       </c>
     </row>
@@ -940,7 +2391,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_STAT_NM</t>
         </is>
       </c>
     </row>
@@ -952,7 +2403,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_STAT_NM</t>
+          <t>Warning in test relationships_CRM_MEMBER_DEV_CMPGN_CD__CMPGN_CD__ref_CRM_CAMPAIGN_</t>
         </is>
       </c>
     </row>
@@ -964,7 +2415,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_MEMBER_DEV_CMPGN_CD__CMPGN_CD__ref_CRM_CAMPAIGN_</t>
+          <t>Warning in test warn_bigquery_load_gap</t>
         </is>
       </c>
     </row>
@@ -1012,7 +2463,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Warning in test assert_fap_ad_ctgr_consistency</t>
+          <t>Warning in test relationships_BIGQUERY_IDENTITY_MBER_NO__MEMBER_DK__ref_CRM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1024,7 +2475,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Warning in test relationships_FACT_MEMBER_FEE_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
+          <t>Warning in test assert_fap_ad_ctgr_consistency</t>
         </is>
       </c>
     </row>
@@ -1036,7 +2487,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Warning in test warn_fmm_reason_unmapped_f_rows</t>
+          <t>Warning in test relationships_FACT_MEMBER_FEE_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1048,7 +2499,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Warning in test relationships_FACT_MEMBER_MONTHLY_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
+          <t>Warning in test relationships_FACT_UNPAID_SERVICE_CONV_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1060,7 +2511,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Warning in test warn_gold_view_comment_coverage</t>
+          <t>Warning in test warn_fmm_reason_unmapped_f_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warning in test relationships_FACT_MEMBER_MONTHLY_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1075,13 +2538,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1115,7 +2578,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-20 07:32:19.186000-07:00</t>
+          <t>2026-10-21 06:05:14.569000+09:00</t>
         </is>
       </c>
     </row>
@@ -1132,7 +2595,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-20 07:32:19.166000-07:00</t>
+          <t>2026-10-21 06:05:14.864000+09:00</t>
         </is>
       </c>
     </row>
@@ -1149,7 +2612,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-20 07:32:19.420000-07:00</t>
+          <t>2026-10-21 06:05:17.149000+09:00</t>
         </is>
       </c>
     </row>
@@ -1166,14 +2629,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:00.884000-07:00</t>
+          <t>2026-10-21 06:07:43.277000+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WARN_GOLD_VIEW_COMMENT_COVERAGE</t>
+          <t>ACCEPTED_VALUES_FACT_EVENT_PAR_3E4477EFE5BD670B9BD4E7A6AA7935A7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1183,7 +2646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-20 07:42:58.460000-07:00</t>
+          <t>2026-08-31 09:35:33.212000+09:00</t>
         </is>
       </c>
     </row>
@@ -1200,7 +2663,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-20 07:42:07.385000-07:00</t>
+          <t>2026-10-21 12:55:51.464000+09:00</t>
         </is>
       </c>
     </row>
@@ -1217,7 +2680,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:30:32.532000-07:00</t>
+          <t>2026-10-21 06:02:04.054000+09:00</t>
         </is>
       </c>
     </row>
@@ -1234,7 +2697,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-20 07:30:32.751000-07:00</t>
+          <t>2026-10-21 06:02:04.053000+09:00</t>
         </is>
       </c>
     </row>
@@ -1251,7 +2714,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-20 07:38:14.768000-07:00</t>
+          <t>2026-10-21 06:15:08.649000+09:00</t>
         </is>
       </c>
     </row>
@@ -1268,24 +2731,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-20 07:42:51.872000-07:00</t>
+          <t>2026-10-21 12:57:27.724000+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>WARN_GOLD_VIEW_COMMENT_COVERAGE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:57:35.077000+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>WARN_SPNSR_CLS_AGGR_SRC_DUP</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-10-20 07:30:33.915000-07:00</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:02:05.437000+09:00</t>
         </is>
       </c>
     </row>
@@ -1306,7 +2786,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1535,7 +3015,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1660,12 +3140,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1582092.0</t>
+          <t>1582580.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3831.0</t>
+          <t>-3343.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1687,12 +3167,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>933717.0</t>
+          <t>934003.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30653.0</t>
+          <t>30939.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1714,12 +3194,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>946965530131.0</t>
+          <t>946990571631.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51787221023.0</t>
+          <t>51812262523.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1741,12 +3221,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>960986496575.0</t>
+          <t>960991921575.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>69026705687.0</t>
+          <t>69032130687.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1903,12 +3383,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4062074.4714</t>
+          <t>4063139.1214</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1770196.4714000002</t>
+          <t>1771261.1214</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1930,12 +3410,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1076739.0</t>
+          <t>1077085.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>38477.0</t>
+          <t>38823.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1957,12 +3437,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1003161.0</t>
+          <t>1003971.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-130965.0</t>
+          <t>-130155.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1984,12 +3464,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>319900.0</t>
+          <t>320014.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-87323.0</t>
+          <t>-87209.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2038,12 +3518,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>44490520.0</t>
+          <t>44496431.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6019740.0</t>
+          <t>6025651.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2065,12 +3545,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1064999.0</t>
+          <t>1065598.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33028.0</t>
+          <t>33627.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2123,7 +3603,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2268,7 +3748,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py SR61467 · 2026-10-21 07:43 KST · 입력 = _ENV/SR61467/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5/12 테이블에 행 있음</t>
+          <t>6/13 테이블에 행 있음</t>
         </is>
       </c>
     </row>
@@ -543,13 +543,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -593,29 +593,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01c7b830-0002-2ae9-0001-72de0563c3a2</t>
+          <t>01c7dd2d-0002-365d-0001-72de071db1be</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12:17.019000+09:00</t>
+          <t>2026-10-21 06:01:00.616000+09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12:36.666000+09:00</t>
+          <t>2026-10-21 06:17:33.068000+09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>--select AGENCY_AD_ROW_DGT+</t>
-        </is>
-      </c>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -626,17 +622,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01c7b830-0002-2ae9-0001-72de0563c4fa</t>
+          <t>01c7de96-0002-365d-0001-72de073035ce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12:43.108000+09:00</t>
+          <t>2026-10-21 12:02:45.704000+09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12:43.356000+09:00</t>
+          <t>2026-10-21 12:03:21.591000+09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -646,34 +642,30 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>--select AGENCY_AD_ROW_DGT+</t>
+          <t>--select FACT_MEMBER_COHORT_SURVIVAL DIM_SEND_REQUEST DIM_MSG_TEMPLATE DIM_MSG_TEMPLATE_BUTTON</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNHANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No active warehouse selected in the current session.  Select an active warehouse with the 'use warehouse' command. ⏎ </t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01c7b830-0002-2984-0001-72de0563f062</t>
+          <t>01c7dea9-0002-365d-0001-72de07316e62</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12:53.485000+09:00</t>
+          <t>2026-10-21 12:21:03.618000+09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-14 16:13:41.767000+09:00</t>
+          <t>2026-10-21 12:22:03.139000+09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -683,7 +675,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>--select AGENCY_AD_ROW_DGT+</t>
+          <t>--select FACT_AD_INFLOW_ALLOC FACT_MEMBER_EVENT_COHORT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -696,17 +688,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01c7b836-0002-2984-0001-72de05645a6a</t>
+          <t>01c7dec2-0002-365d-0001-72de07333032</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 16:18:51.261000+09:00</t>
+          <t>2026-10-21 12:46:00.189000+09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-14 16:19:37.364000+09:00</t>
+          <t>2026-10-21 12:57:40.504000+09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -716,7 +708,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>--select AGENCY_AD_ROW_DGT+ AGENCY_AD_CREATIVE+ AGENCY_AD_PERFORMANCE+ AGENCY_AD_DIGITAL+</t>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -729,17 +721,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01c7bb6d-0002-2c93-0001-72de058b884e</t>
+          <t>01c7e2cd-0002-3693-0001-72de07617672</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 06:01:01.813000+09:00</t>
+          <t>2026-10-22 06:01:00.716000+09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-15 06:10:56.123000+09:00</t>
+          <t>2026-10-22 06:18:32.203000+09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -750,25 +742,29 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 718 total (total time: 1020.64s) ⏎ First error in model 'CRM_HOLIDAY': Database Error in model CRM_HOLIDAY (models/silver/crm/CRM_HOLIDAY.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on schema 'SILVER'. Your primary role GN_DW_DBT must have CREATE TABLE granted on SCHEMA GN_DW.SILVER. ⏎   compiled code at /tmp/dbt_output/target/run/gn_dw_silver/models/silver/crm/CRM_HOLIDAY.sql.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7e2cd-0002-3693-0001-72de07617672') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01c7bba3-0002-2d5f-0001-72de058e7416</t>
+          <t>01c7e4ad-0002-3719-0001-72de0777a28e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-15 06:55:56.049000+09:00</t>
+          <t>2026-10-22 14:01:24.228000+09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-15 06:56:13.673000+09:00</t>
+          <t>2026-10-22 14:01:44.821000+09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -787,17 +783,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01c7bba4-0002-2ae9-0001-72de058e56aa</t>
+          <t>01c7e4ad-0002-3866-0001-72de07769bfe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-15 06:56:14.799000+09:00</t>
+          <t>2026-10-22 14:01:45.590000+09:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-15 06:56:36.646000+09:00</t>
+          <t>2026-10-22 14:02:09.954000+09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -816,17 +812,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01c7bba4-0002-2d5f-0001-72de058e76c2</t>
+          <t>01c7e4ae-0002-3780-0001-72de07779dca</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-15 06:56:38.242000+09:00</t>
+          <t>2026-10-22 14:02:11.226000+09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-15 07:05:46.848000+09:00</t>
+          <t>2026-10-22 14:15:17.281000+09:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -837,25 +833,29 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎ [0m05:15:08  Got 1 result, configured to warn if != 0 ⏎ [0m05:15:08   ⏎ [0m05:15:08    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_gold_view_comment_coverage.sql ⏎ [0m05:15:08   ⏎ [0m05:15:08    See test failures: ⏎   ------------------------------------------------------- ⏎   select * from GN_DW.OPS.warn_gold_view_comment_coverage ⏎   ------------------------------------------------------- ⏎ [0m05:15:08   ⏎ [0m05:15:08  Done. PASS=706 WARN=22 ERROR=1 SKIP=0 TOTAL=729. ⏎  Run select system$get_dbt_log('01c7e4ae-0002-3780-0001-72de07779dca') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01c7bbae-0002-2cbb-0001-72de058f3772</t>
+          <t>01c7e56c-0002-38d7-0001-72de0781d09e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-15 07:06:36.526000+09:00</t>
+          <t>2026-10-22 17:12:14.785000+09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-15 07:10:16.760000+09:00</t>
+          <t>2026-10-22 18:20:04.833000+09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -878,17 +878,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01c7bc66-0002-2d8a-0001-72de0598c9f2</t>
+          <t>01c7e5b1-0002-38d2-0001-72de07847fd6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-15 10:10:13.618000+09:00</t>
+          <t>2026-10-22 18:21:44.366000+09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-15 10:10:37.658000+09:00</t>
+          <t>2026-10-22 18:42:50.784000+09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -896,32 +896,32 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>--select DIM_MARKETING_CAMPAIGN</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1236.44s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7e5b1-0002-38d2-0001-72de07847fd6') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01c7bce8-0002-2d5f-0001-72de05a015de</t>
+          <t>01c7e86d-0002-38ee-0001-72de0795c412</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-15 12:20:54.911000+09:00</t>
+          <t>2026-10-23 06:01:00.592000+09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-15 12:24:42.395000+09:00</t>
+          <t>2026-10-23 06:18:47.355000+09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -937,29 +937,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DBT job failed: 4 model(s) failed out of 656 total (total time: 206.62s) ⏎ First error in model 'CRM_SEND_MEMBER': Database Error in model CRM_SEND_MEMBER (models/silver/crm/CRM_SEND_MEMBER.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'CRM_SEND_MEMBER'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.SILVER.CRM_SEND_MEMBER. ⏎ Error 2 in model 'DIM_CAMPAIGN': Database Error in model DIM_CAMPAIGN (models/gold/dim/DIM_CAMPAIGN.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'DIM_CAMPAIGN'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.GOLD.DIM_CAMPAIGN. ⏎ Error 3 in model 'FACT_EXPENSE_RESOLUTION': Database Error in model FACT_EXPENSE_RESOLUTION (models/gold/fact/FACT_EXPENSE_RESOLUTION.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'FACT_EXPENSE_RESOLUTION'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.GOLD.FACT_EXPENSE_RESOLUTION. ⏎ Error 4 in model 'FACT_AD_PERFORMANCE': Database Error in model FACT_AD_PERFORMANCE (models/gold/fact/FACT_AD_PERFORMANCE.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'FACT_AD_PERFORMANCE'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.GOLD.FACT_AD_PERFORMANCE..  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7bce8-0002-2d5f-0001-72de05a015de') for more details.</t>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1036.86s) ⏎ First error in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM' ⏎ Error 2 in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7e86d-0002-38ee-0001-72de0795c412') for more details.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01c7bcfb-0002-2d5f-0001-72de05a14056</t>
+          <t>01c7ee0d-0002-3b62-0001-72de07cf04de</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-15 12:39:51.192000+09:00</t>
+          <t>2026-10-24 06:01:00.753000+09:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-15 12:40:21.176000+09:00</t>
+          <t>2026-10-24 06:18:43.783000+09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>retry</t>
+          <t>build</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -970,24 +970,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DBT job failed. Last output lines: ⏎ [0m03:40:19    Got 271489 results, configured to fail if != 0 ⏎ [0m03:40:19   ⏎ [0m03:40:19    compiled code at target/compiled/gn_dw_silver/models/gold/_gold_ready_schema.yml/relationships_FACT_AD_PERFORMA_113fefc940e6a2beee03c97acac8ee59.sql ⏎ [0m03:40:19   ⏎ [0m03:40:20  [33mWarning in test warn_fap_mktg_unmapped_ratio (tests/warn_fap_mktg_unmapped_ratio.sql)[0m ⏎ [0m03:40:20  Got 1 result, configured to warn if != 0 ⏎ [0m03:40:20   ⏎ [0m03:40:20    compiled code at target/compiled/gn_dw_silver/tests/warn_fap_mktg_unmapped_ratio.sql ⏎ [0m03:40:20   ⏎ [0m03:40:20  Done. PASS=32 WARN=1 ERROR=7 SKIP=78 TOTAL=118. ⏎  Run select system$get_dbt_log('01c7bcfb-0002-2d5f-0001-72de05a14056') for more details.</t>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1031.37s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7ee0d-0002-3b62-0001-72de07cf04de') for more details.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01c7bcff-0002-2d6f-0001-72de05a14002</t>
+          <t>01c7f3ad-0002-3dfd-0001-72de07fc9042</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-15 12:43:58.942000+09:00</t>
+          <t>2026-10-25 06:01:06.262000+09:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-15 12:54:02.042000+09:00</t>
+          <t>2026-10-25 06:19:21.073000+09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1003,24 +1003,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DBT job failed: 1 model(s) failed out of 656 total (total time: 576.62s) ⏎ First error in model 'CRM_SEND_MEMBER': Database Error in model CRM_SEND_MEMBER (models/silver/crm/CRM_SEND_MEMBER.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'CRM_SEND_MEMBER'. Your primary role GN_DW_DBT must have MODIFY granted on TABLE GN_DW.SILVER.CRM_SEND_MEMBER..  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7bcff-0002-2d6f-0001-72de05a14002') for more details.</t>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1060.60s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7f3ad-0002-3dfd-0001-72de07fc9042') for more details.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01c7bd29-0002-2d8a-0001-72de05a3afd2</t>
+          <t>01c7f94d-0002-3e97-0001-72de0816f7b6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-15 13:25:27.299000+09:00</t>
+          <t>2026-10-26 06:01:01.622000+09:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-15 13:36:50.025000+09:00</t>
+          <t>2026-10-26 06:19:12.923000+09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1031,25 +1031,29 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1058.38s) ⏎ First error in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM' ⏎ Error 2 in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7f94d-0002-3e97-0001-72de0816f7b6') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01c7c07d-0002-2f20-0001-72de05d186e6</t>
+          <t>01c7fc46-0002-410b-0001-72de08309a62</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-16 03:37:48.576000+09:00</t>
+          <t>2026-10-26 18:42:39.203000+09:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-16 03:38:10.317000+09:00</t>
+          <t>2026-10-26 18:42:58.436000+09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1068,17 +1072,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01c7c07e-0002-2f1f-0001-72de05d16986</t>
+          <t>01c7fc47-0002-410b-0001-72de08309c4a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-16 03:38:14.183000+09:00</t>
+          <t>2026-10-26 18:43:05.592000+09:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-16 03:38:37.133000+09:00</t>
+          <t>2026-10-26 18:43:29.166000+09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1097,22 +1101,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01c7c07e-0002-2f16-0001-72de05d198f6</t>
+          <t>01c7fc47-0002-410b-0001-72de08309e5a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-16 03:38:38.072000+09:00</t>
+          <t>2026-10-26 18:43:30.489000+09:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-16 03:51:04.487000+09:00</t>
+          <t>2026-10-26 18:43:48.890000+09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1126,17 +1130,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01c7c09f-0002-2f1f-0001-72de05d40046</t>
+          <t>01c7fc47-0002-410b-0001-72de0830c0f2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-16 04:11:06.158000+09:00</t>
+          <t>2026-10-26 18:43:49.918000+09:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-16 04:11:37.208000+09:00</t>
+          <t>2026-10-26 18:57:47.586000+09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1144,36 +1148,28 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>--select FACT_AD_PERFORMANCE</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>DBT job failed. Last output lines: ⏎ [0m19:11:35    Got 271489 results, configured to fail if != 0 ⏎ [0m19:11:35   ⏎ [0m19:11:35    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/models/gold/_gold_ready_schema.yml/relationships_FACT_AD_PERFORMA_113fefc940e6a2beee03c97acac8ee59.sql ⏎ [0m19:11:35   ⏎ [0m19:11:35  [33mWarning in test warn_fap_mktg_unmapped_ratio (tests/warn_fap_mktg_unmapped_ratio.sql)[0m ⏎ [0m19:11:35  Got 1 result, configured to warn if != 0 ⏎ [0m19:11:35   ⏎ [0m19:11:35    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fap_mktg_unmapped_ratio.sql ⏎ [0m19:11:35   ⏎ [0m19:11:35  Done. PASS=15 WARN=1 ERROR=4 SKIP=0 TOTAL=20. ⏎  Run select system$get_dbt_log('01c7c09f-0002-2f1f-0001-72de05d40046') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01c7c0a0-0002-2f1f-0001-72de05d4057a</t>
+          <t>01c7fc55-0002-410b-0001-72de083198b6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-16 04:12:01.280000+09:00</t>
+          <t>2026-10-26 18:57:54.107000+09:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-16 04:12:54.537000+09:00</t>
+          <t>2026-10-26 20:05:43.892000+09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1183,39 +1179,35 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>--select +FACT_AD_PERFORMANCE+</t>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>DBT job failed. Last output lines: ⏎   ---------------------------------------------- ⏎   select * from GN_DW.OPS.warn_bigquery_load_gap ⏎   ---------------------------------------------- ⏎ [0m19:12:51   ⏎ [0m19:12:51  [33mWarning in test warn_fer_mktg_campaign_multi (tests/warn_fer_mktg_campaign_multi.sql)[0m ⏎ [0m19:12:51  Got 1 result, configured to warn if != 0 ⏎ [0m19:12:51   ⏎ [0m19:12:51    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fer_mktg_campaign_multi.sql ⏎ [0m19:12:51   ⏎ [0m19:12:51  Done. PASS=89 WARN=5 ERROR=2 SKIP=5 TOTAL=101. ⏎  Run select system$get_dbt_log('01c7c0a0-0002-2f1f-0001-72de05d4057a') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01c7c0a1-0002-2f1f-0001-72de05d4354e</t>
+          <t>01c7feed-0002-41a1-0001-72de084be766</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-16 04:13:19.052000+09:00</t>
+          <t>2026-10-27 06:01:00.848000+09:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-16 04:13:31.999000+09:00</t>
+          <t>2026-10-27 06:23:04.031000+09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>parse</t>
+          <t>build</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1229,22 +1221,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01c7c0a1-0002-2f1f-0001-72de05d43636</t>
+          <t>01c80020-0002-41a1-0001-72de085a6e12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-16 04:13:34.397000+09:00</t>
+          <t>2026-10-27 11:08:49.908000+09:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-16 04:13:56.204000+09:00</t>
+          <t>2026-10-27 11:09:13.146000+09:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>compile</t>
+          <t>parse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1258,22 +1250,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01c7c0a2-0002-2f20-0001-72de05d443b2</t>
+          <t>01c80021-0002-41fc-0001-72de085a991e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-16 04:14:03.543000+09:00</t>
+          <t>2026-10-27 11:09:14.090000+09:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-16 04:25:38.673000+09:00</t>
+          <t>2026-10-27 11:09:39.225000+09:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>compile</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1287,22 +1279,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01c7c0bb-0002-2f16-0001-72de05d5f79a</t>
+          <t>01c80021-0002-41fc-0001-72de085a9d5a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-16 04:39:47.441000+09:00</t>
+          <t>2026-10-27 11:09:48.849000+09:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-16 04:40:07.752000+09:00</t>
+          <t>2026-10-27 11:10:07.891000+09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>parse</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1316,883 +1308,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01c7c0bc-0002-2f20-0001-72de05d5eef6</t>
+          <t>01c80022-0002-41fc-0001-72de085ad02e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-16 04:40:14.586000+09:00</t>
+          <t>2026-10-27 11:10:08.883000+09:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-16 04:40:17.700000+09:00</t>
+          <t>2026-10-27 11:12:46.976000+09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>compile</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNHANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>SQL execution canceled</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>01c7c0be-0002-2f20-0001-72de05d628ae</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:42:13.273000+09:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:42:31.219000+09:00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>01c7c0be-0002-2f1f-0001-72de05d61fb2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:42:32.900000+09:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:42:54.690000+09:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>compile</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>01c7c0be-0002-2f20-0001-72de05d62c72</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:42:56.364000+09:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:54:34.343000+09:00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>01c7c10d-0002-2f1f-0001-72de05dae2a2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-10-16 06:01:00.683000+09:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-10-16 06:12:44.758000+09:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>01c7c399-0002-2f1f-0001-72de0600c2aa</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-16 16:53:37.341000+09:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:19:33.229000+09:00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DBT job failed. Last output lines: ⏎   --------------------------------------------------------------------------------------- ⏎   select * from GN_DW.OPS.accepted_values_FACT_EVENT_ATT_a31e050516c23794739ccbd32aaa8c43 ⏎   --------------------------------------------------------------------------------------- ⏎ [0m08:19:21   ⏎ [0m08:19:21  [33mWarning in test warn_fmm_reason_unmapped_f_rows (tests/warn_fmm_reason_unmapped_f_rows.sql)[0m ⏎ [0m08:19:21  Got 1 result, configured to warn if != 0 ⏎ [0m08:19:21   ⏎ [0m08:19:21    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fmm_reason_unmapped_f_rows.sql ⏎ [0m08:19:21   ⏎ [0m08:19:21  Done. PASS=628 WARN=19 ERROR=8 SKIP=24 TOTAL=679. ⏎  Run select system$get_dbt_log('01c7c399-0002-2f1f-0001-72de0600c2aa') for more details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>01c7c39a-0002-2f20-0001-72de0600b6de</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-10-16 16:54:02.224000+09:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:21:22.768000+09:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DBT job failed. Last output lines: ⏎   --------------------------------------------------------------------------------------- ⏎   select * from GN_DW.OPS.accepted_values_FACT_EVENT_ATT_a31e050516c23794739ccbd32aaa8c43 ⏎   --------------------------------------------------------------------------------------- ⏎ [0m08:21:09   ⏎ [0m08:21:09  [33mWarning in test warn_fmm_reason_unmapped_f_rows (tests/warn_fmm_reason_unmapped_f_rows.sql)[0m ⏎ [0m08:21:09  Got 1 result, configured to warn if != 0 ⏎ [0m08:21:09   ⏎ [0m08:21:09    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fmm_reason_unmapped_f_rows.sql ⏎ [0m08:21:09   ⏎ [0m08:21:09  Done. PASS=630 WARN=19 ERROR=6 SKIP=24 TOTAL=679. ⏎  Run select system$get_dbt_log('01c7c39a-0002-2f20-0001-72de0600b6de') for more details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>01c7c3bb-0002-314b-0001-72de0603c88e</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:27:01.224000+09:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:27:18.931000+09:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>01c7c3bb-0002-30d2-0001-72de0603ab7a</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:27:19.974000+09:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:27:41.717000+09:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>compile</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>01c7c3bb-0002-2f16-0001-72de0603ba66</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:27:42.453000+09:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:40:03.854000+09:00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>01c7c4c7-0002-2f16-0001-72de0613769a</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:55:17.928000+09:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:55:36.347000+09:00</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>01c7c4c7-0002-2f16-0001-72de06137792</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:55:38.249000+09:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:55:59.819000+09:00</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>compile</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>01c7c4c8-0002-2f1f-0001-72de061391f2</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:56:01.399000+09:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:08:19.475000+09:00</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>DBT job failed. Last output lines: ⏎ [0m13:08:08  Got 1 result, configured to warn if != 0 ⏎ [0m13:08:08   ⏎ [0m13:08:08    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_fmm_reason_unmapped_f_rows.sql ⏎ [0m13:08:08   ⏎ [0m13:08:08  [33mWarning in test relationships_FACT_MEMBER_MONTHLY_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_ (models/gold/_gold_ready_schema.yml)[0m ⏎ [0m13:08:08  Got 181 results, configured to warn if != 0 ⏎ [0m13:08:08   ⏎ [0m13:08:08    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/models/gold/_gold_ready_schema.yml/relationships_FACT_MEMBER_MONT_53f1dbedc04314fed8831c443e382e05.sql ⏎ [0m13:08:08   ⏎ [0m13:08:08  Done. PASS=672 WARN=21 ERROR=1 SKIP=6 TOTAL=700. ⏎  Run select system$get_dbt_log('01c7c4c8-0002-2f1f-0001-72de061391f2') for more details.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>01c7c4ec-0002-30d2-0001-72de0616c5d6</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:32:45.118000+09:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:33:04.310000+09:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>01c7c4ed-0002-314b-0001-72de0616d25e</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:33:04.646000+09:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:33:26.918000+09:00</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>compile</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>01c7c4ed-0002-2f20-0001-72de0616f126</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:33:27.921000+09:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:46:07.600000+09:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>01c7c6ad-0002-2f20-0001-72de0630252e</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-10-17 06:01:00.819000+09:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-10-17 06:14:30.929000+09:00</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>01c7cc4d-0002-314d-0001-72de067a061a</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-10-18 06:01:00.853000+09:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-10-18 06:13:53.565000+09:00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>01c7d0bf-0002-32bf-0001-72de06abc732</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-10-19 00:59:46.644000+09:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00:05.432000+09:00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>01c7d0c0-0002-3248-0001-72de06abbb46</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00:06.331000+09:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00:32.468000+09:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>compile</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>01c7d0c0-0002-3248-0001-72de06abbe26</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00:33.904000+09:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:13:30.483000+09:00</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>01c7d0cd-0002-3274-0001-72de06acd4fa</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:13:37.433000+09:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:23:21.095000+09:00</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>UNHANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>SQL execution canceled</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>01c7d0d8-0002-3274-0001-72de06ad2e02</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:24:21.420000+09:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-10-19 02:28:10.772000+09:00</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>01c7d1ed-0002-32bf-0001-72de06b76066</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-10-19 06:01:00.817000+09:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-10-19 06:17:23.432000+09:00</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>01c7d78d-0002-35c4-0001-72de06e1f6c2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:01:00.820000+09:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:17:20.799000+09:00</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>01c7dd2d-0002-365d-0001-72de071db1be</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-10-21 06:01:00.616000+09:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-10-21 06:17:33.068000+09:00</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>01c7de96-0002-365d-0001-72de073035ce</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:02:45.704000+09:00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:03:21.591000+09:00</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>--select FACT_MEMBER_COHORT_SURVIVAL DIM_SEND_REQUEST DIM_MSG_TEMPLATE DIM_MSG_TEMPLATE_BUTTON</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>01c7dea9-0002-365d-0001-72de07316e62</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:21:03.618000+09:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:22:03.139000+09:00</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>--select FACT_AD_INFLOW_ALLOC FACT_MEMBER_EVENT_COHORT</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>01c7dec2-0002-365d-0001-72de07333032</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:46:00.189000+09:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:57:40.504000+09:00</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2211,7 +1351,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2538,13 +1678,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2568,24 +1708,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NOT_NULL_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
+          <t>NOT_NULL_WIDE_MBRFEE_PRDT_ACTL_DATA_TYPE_STD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-21 06:05:14.569000+09:00</t>
+          <t>2026-10-27 11:11:43.732000+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NOT_NULL_CRM_EVENT_PARTICIPATION_PARTCPT_PATH_NM</t>
+          <t>NOT_NULL_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2595,14 +1735,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-21 06:05:14.864000+09:00</t>
+          <t>2026-10-27 11:10:57.486000+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NOT_NULL_CRM_EVENT_PARTICIPATION_PARTCPT_STAT_NM</t>
+          <t>NOT_NULL_CRM_EVENT_PARTICIPATION_PARTCPT_PATH_NM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2612,31 +1752,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-21 06:05:17.149000+09:00</t>
+          <t>2026-10-27 11:10:57.506000+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACCEPTED_VALUES_FACT_EVENT_ATT_A31E050516C23794739CCBD32AAA8C43</t>
+          <t>NOT_NULL_CRM_EVENT_PARTICIPATION_PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-21 06:07:43.277000+09:00</t>
+          <t>2026-10-27 11:10:57.482000+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACCEPTED_VALUES_FACT_EVENT_PAR_3E4477EFE5BD670B9BD4E7A6AA7935A7</t>
+          <t>ACCEPTED_VALUES_FACT_EVENT_ATT_A31E050516C23794739CCBD32AAA8C43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2646,31 +1786,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-31 09:35:33.212000+09:00</t>
+          <t>2026-10-27 11:10:35.808000+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WARN_BIGQUERY_LOAD_GAP</t>
+          <t>ACCEPTED_VALUES_FACT_EVENT_PAR_3E4477EFE5BD670B9BD4E7A6AA7935A7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-21 12:55:51.464000+09:00</t>
+          <t>2026-08-31 09:35:33.212000+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID</t>
+          <t>WARN_BIGQUERY_LOAD_GAP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2680,14 +1820,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-21 06:02:04.054000+09:00</t>
+          <t>2026-10-27 11:12:32.583000+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID_ROWS</t>
+          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2697,14 +1837,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-21 06:02:04.053000+09:00</t>
+          <t>2026-10-27 11:12:27.438000+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WARN_FMM_FUTURE_MONTH_CAP</t>
+          <t>WARN_BIGQUERY_NULL_USER_PSEUDO_ID_ROWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2714,14 +1854,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-21 06:15:08.649000+09:00</t>
+          <t>2026-10-27 11:12:27.923000+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WARN_GOLD_FACT_BIGQUERY_DATE_SK_ZERO</t>
+          <t>WARN_FMM_FUTURE_MONTH_CAP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2731,14 +1871,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-21 12:57:27.724000+09:00</t>
+          <t>2026-10-27 11:12:32.031000+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WARN_GOLD_VIEW_COMMENT_COVERAGE</t>
+          <t>WARN_GOLD_FACT_BIGQUERY_DATE_SK_ZERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2748,24 +1888,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-21 12:57:35.077000+09:00</t>
+          <t>2026-10-27 11:12:32.663000+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>WARN_GOLD_VIEW_COMMENT_COVERAGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:12:37.655000+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>WARN_SPNSR_CLS_AGGR_SRC_DUP</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-10-21 06:02:05.437000+09:00</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:12:33.769000+09:00</t>
         </is>
       </c>
     </row>
@@ -2786,7 +1943,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -3015,7 +2172,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -3140,12 +2297,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1582580.0</t>
+          <t>1584428.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3343.0</t>
+          <t>-1495.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3167,12 +2324,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>934003.0</t>
+          <t>935034.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30939.0</t>
+          <t>31970.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3194,12 +2351,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>946990571631.0</t>
+          <t>947093601916.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51812262523.0</t>
+          <t>51915292808.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3221,12 +2378,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>960991921575.0</t>
+          <t>961981566649.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>69032130687.0</t>
+          <t>70021775761.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3248,12 +2405,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>85.767702</t>
+          <t>85.767719</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.000549000000006572</t>
+          <t>0.0005660000000062837</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3383,12 +2540,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4063139.1214</t>
+          <t>4067856.2614</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1771261.1214</t>
+          <t>1775978.2614000002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3410,12 +2567,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1077085.0</t>
+          <t>1078353.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>38823.0</t>
+          <t>40091.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3437,12 +2594,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1003971.0</t>
+          <t>1009981.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-130155.0</t>
+          <t>-124145.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3464,12 +2621,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>320014.0</t>
+          <t>320845.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-87209.0</t>
+          <t>-86378.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3518,12 +2675,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>44496431.0</t>
+          <t>44646949.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6025651.0</t>
+          <t>6176169.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3545,12 +2702,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1065598.0</t>
+          <t>1067787.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33627.0</t>
+          <t>35816.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3603,7 +2760,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -3748,7 +2905,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-21 13:27 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PASS 678 · WARN 24 · ERROR 0 · SKIP 0</t>
+          <t>PASS 735 · WARN 26 · ERROR 0 · SKIP 0</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Done. PASS=678 WARN=24 ERROR=0 SKIP=0 TOTAL=702</t>
+          <t>Done. PASS=735 WARN=26 ERROR=0 SKIP=0 TOTAL=761</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_PAYMENT_BILLING_MBER_NO</t>
+          <t>Warning in test warn_map_coverage_ext_data_type</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_PAYMENT_BILLING_RQEST_RST_CD</t>
+          <t>Warning in test not_null_CRM_PAYMENT_BILLING_MBER_NO</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_PAYMENT_BILLING_SPNSR_BSNS_ID__SPNSR_BSNS_ID__ref_CRM_SPONSORSHIP_</t>
+          <t>Warning in test not_null_CRM_PAYMENT_BILLING_RQEST_RST_CD</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Warning in test warn_erp_budget_month_grain</t>
+          <t>Warning in test relationships_CRM_PAYMENT_BILLING_SPNSR_BSNS_ID__SPNSR_BSNS_ID__ref_CRM_SPONSORSHIP_</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_CAMPAIGN_SPNSR_BSNS_ID__SPNSR_BSNS_ID__ref_CRM_SPONSORSHIP_</t>
+          <t>Warning in test warn_erp_budget_month_grain</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_MEMBER_CMPGN_CD__CMPGN_CD__ref_CRM_CAMPAIGN_</t>
+          <t>Warning in test relationships_CRM_CAMPAIGN_SPNSR_BSNS_ID__SPNSR_BSNS_ID__ref_CRM_SPONSORSHIP_</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_PAYMENT_BILLING_MBER_NO__MEMBER_DK__ref_CRM_MEMBER_</t>
+          <t>Warning in test relationships_CRM_MEMBER_CMPGN_CD__CMPGN_CD__ref_CRM_CAMPAIGN_</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
+          <t>Warning in test relationships_CRM_PAYMENT_BILLING_MBER_NO__MEMBER_DK__ref_CRM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_PATH_NM</t>
+          <t>Warning in test not_null_WIDE_MBRFEE_PRDT_ACTL_DATA_TYPE_STD</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_STAT_NM</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_CHNNL_NM</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_MEMBER_DEV_CMPGN_CD__CMPGN_CD__ref_CRM_CAMPAIGN_</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_PATH_NM</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Warning in test warn_bigquery_load_gap</t>
+          <t>Warning in test not_null_CRM_EVENT_PARTICIPATION_PARTCPT_STAT_NM</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Warning in test not_null_CRM_SEND_MEMBER_SEND_RESULT_NAME</t>
+          <t>Warning in test relationships_CRM_MEMBER_DEV_CMPGN_CD__CMPGN_CD__ref_CRM_CAMPAIGN_</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Warning in test relationships_CRM_SEND_MEMBER_SNDNG_KEY__SNDNG_KEY__ref_CRM_SEND_REQUEST_</t>
+          <t>Warning in test not_null_CRM_SEND_MEMBER_SEND_RESULT_NAME</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Warning in test accepted_values_FACT_EVENT_ATTENDANCE_PART_STATUS__1__2__3__4__5__6__110__120__130__140__150__160__170__180__190__200__210__220</t>
+          <t>Warning in test relationships_CRM_SEND_MEMBER_SNDNG_KEY__SNDNG_KEY__ref_CRM_SEND_REQUEST_</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Warning in test relationships_BIGQUERY_IDENTITY_MBER_NO__MEMBER_DK__ref_CRM_MEMBER_</t>
+          <t>Warning in test accepted_values_FACT_EVENT_ATTENDANCE_PART_STATUS__1__2__3__4__5__6__110__120__130__140__150__160__170__180__190__200__210__220</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Warning in test assert_fap_ad_ctgr_consistency</t>
+          <t>Warning in test relationships_FACT_MEMBER_FEE_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Warning in test relationships_FACT_MEMBER_FEE_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
+          <t>Warning in test relationships_BIGQUERY_IDENTITY_MBER_NO__MEMBER_DK__ref_CRM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Warning in test relationships_FACT_UNPAID_SERVICE_CONV_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
+          <t>Warning in test assert_fap_ad_ctgr_consistency</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Warning in test warn_fmm_reason_unmapped_f_rows</t>
+          <t>Warning in test relationships_FACT_UNPAID_SERVICE_CONV_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Warning in test warn_fmm_reason_unmapped_f_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Warning in test relationships_FACT_MEMBER_MONTHLY_MEMBER_DK__MEMBER_DK__ref_DIM_MEMBER_</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Warning in test warn_gold_view_comment_coverage</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1708,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1967,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2196,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2784,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2929,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-27 14:23 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N05_테스트결과서.xlsx
@@ -426,7 +426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6/13 테이블에 행 있음</t>
+          <t>7/13 테이블에 행 있음</t>
         </is>
       </c>
     </row>
@@ -543,13 +543,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01c7dd2d-0002-365d-0001-72de071db1be</t>
+          <t>01c7ee0d-0002-3b62-0001-72de07cf04de</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 06:01:00.616000+09:00</t>
+          <t>2026-10-24 06:01:00.753000+09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-21 06:17:33.068000+09:00</t>
+          <t>2026-10-24 06:18:43.783000+09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -614,25 +614,29 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1031.37s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7ee0d-0002-3b62-0001-72de07cf04de') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01c7de96-0002-365d-0001-72de073035ce</t>
+          <t>01c7f3ad-0002-3dfd-0001-72de07fc9042</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:02:45.704000+09:00</t>
+          <t>2026-10-25 06:01:06.262000+09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:03:21.591000+09:00</t>
+          <t>2026-10-25 06:19:21.073000+09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -640,32 +644,32 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>--select FACT_MEMBER_COHORT_SURVIVAL DIM_SEND_REQUEST DIM_MSG_TEMPLATE DIM_MSG_TEMPLATE_BUTTON</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1060.60s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7f3ad-0002-3dfd-0001-72de07fc9042') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01c7dea9-0002-365d-0001-72de07316e62</t>
+          <t>01c7f94d-0002-3e97-0001-72de0816f7b6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:21:03.618000+09:00</t>
+          <t>2026-10-26 06:01:01.622000+09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:22:03.139000+09:00</t>
+          <t>2026-10-26 06:19:12.923000+09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -673,44 +677,40 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>--select FACT_AD_INFLOW_ALLOC FACT_MEMBER_EVENT_COHORT</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1058.38s) ⏎ First error in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM' ⏎ Error 2 in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7f94d-0002-3e97-0001-72de0816f7b6') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01c7dec2-0002-365d-0001-72de07333032</t>
+          <t>01c7fc46-0002-410b-0001-72de08309a62</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21 12:46:00.189000+09:00</t>
+          <t>2026-10-26 18:42:39.203000+09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-21 12:57:40.504000+09:00</t>
+          <t>2026-10-26 18:42:58.436000+09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
-        </is>
-      </c>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -721,55 +721,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01c7e2cd-0002-3693-0001-72de07617672</t>
+          <t>01c7fc47-0002-410b-0001-72de08309c4a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 06:01:00.716000+09:00</t>
+          <t>2026-10-26 18:43:05.592000+09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-22 06:18:32.203000+09:00</t>
+          <t>2026-10-26 18:43:29.166000+09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>compile</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>DBT job failed: 1 model(s) failed out of 718 total (total time: 1020.64s) ⏎ First error in model 'CRM_HOLIDAY': Database Error in model CRM_HOLIDAY (models/silver/crm/CRM_HOLIDAY.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on schema 'SILVER'. Your primary role GN_DW_DBT must have CREATE TABLE granted on SCHEMA GN_DW.SILVER. ⏎   compiled code at /tmp/dbt_output/target/run/gn_dw_silver/models/silver/crm/CRM_HOLIDAY.sql.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7e2cd-0002-3693-0001-72de07617672') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01c7e4ad-0002-3719-0001-72de0777a28e</t>
+          <t>01c7fc47-0002-410b-0001-72de08309e5a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-22 14:01:24.228000+09:00</t>
+          <t>2026-10-26 18:43:30.489000+09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-22 14:01:44.821000+09:00</t>
+          <t>2026-10-26 18:43:48.890000+09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>parse</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -783,22 +779,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01c7e4ad-0002-3866-0001-72de07769bfe</t>
+          <t>01c7fc47-0002-410b-0001-72de0830c0f2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:01:45.590000+09:00</t>
+          <t>2026-10-26 18:43:49.918000+09:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:02:09.954000+09:00</t>
+          <t>2026-10-26 18:57:47.586000+09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>compile</t>
+          <t>build</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -812,17 +808,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01c7e4ae-0002-3780-0001-72de07779dca</t>
+          <t>01c7fc55-0002-410b-0001-72de083198b6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-22 14:02:11.226000+09:00</t>
+          <t>2026-10-26 18:57:54.107000+09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-22 14:15:17.281000+09:00</t>
+          <t>2026-10-26 20:05:43.892000+09:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,32 +826,32 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>DBT job failed. Last output lines: ⏎ [0m05:15:08  Got 1 result, configured to warn if != 0 ⏎ [0m05:15:08   ⏎ [0m05:15:08    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_gold_view_comment_coverage.sql ⏎ [0m05:15:08   ⏎ [0m05:15:08    See test failures: ⏎   ------------------------------------------------------- ⏎   select * from GN_DW.OPS.warn_gold_view_comment_coverage ⏎   ------------------------------------------------------- ⏎ [0m05:15:08   ⏎ [0m05:15:08  Done. PASS=706 WARN=22 ERROR=1 SKIP=0 TOTAL=729. ⏎  Run select system$get_dbt_log('01c7e4ae-0002-3780-0001-72de07779dca') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01c7e56c-0002-38d7-0001-72de0781d09e</t>
+          <t>01c7feed-0002-41a1-0001-72de084be766</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-22 17:12:14.785000+09:00</t>
+          <t>2026-10-27 06:01:00.848000+09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-22 18:20:04.833000+09:00</t>
+          <t>2026-10-27 06:23:04.031000+09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -863,11 +859,7 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -878,149 +870,133 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01c7e5b1-0002-38d2-0001-72de07847fd6</t>
+          <t>01c80020-0002-41a1-0001-72de085a6e12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-22 18:21:44.366000+09:00</t>
+          <t>2026-10-27 11:08:49.908000+09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-22 18:42:50.784000+09:00</t>
+          <t>2026-10-27 11:09:13.146000+09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>parse</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1236.44s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7e5b1-0002-38d2-0001-72de07847fd6') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01c7e86d-0002-38ee-0001-72de0795c412</t>
+          <t>01c80021-0002-41fc-0001-72de085a991e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-23 06:01:00.592000+09:00</t>
+          <t>2026-10-27 11:09:14.090000+09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-23 06:18:47.355000+09:00</t>
+          <t>2026-10-27 11:09:39.225000+09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>compile</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1036.86s) ⏎ First error in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM' ⏎ Error 2 in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7e86d-0002-38ee-0001-72de0795c412') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01c7ee0d-0002-3b62-0001-72de07cf04de</t>
+          <t>01c80021-0002-41fc-0001-72de085a9d5a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 06:01:00.753000+09:00</t>
+          <t>2026-10-27 11:09:48.849000+09:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 06:18:43.783000+09:00</t>
+          <t>2026-10-27 11:10:07.891000+09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1031.37s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7ee0d-0002-3b62-0001-72de07cf04de') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01c7f3ad-0002-3dfd-0001-72de07fc9042</t>
+          <t>01c80022-0002-41fc-0001-72de085ad02e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 06:01:06.262000+09:00</t>
+          <t>2026-10-27 11:10:08.883000+09:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-25 06:19:21.073000+09:00</t>
+          <t>2026-10-27 11:12:46.976000+09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1060.60s) ⏎ First error in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD' ⏎ Error 2 in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7f3ad-0002-3dfd-0001-72de07fc9042') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01c7f94d-0002-3e97-0001-72de0816f7b6</t>
+          <t>01c8048d-0002-4354-0001-72de0896402e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-26 06:01:01.622000+09:00</t>
+          <t>2026-10-28 06:01:00.602000+09:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-26 06:19:12.923000+09:00</t>
+          <t>2026-10-28 06:18:56.103000+09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1031,29 +1007,25 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HANDLED_ERROR</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DBT job failed: 2 model(s) failed out of 729 total (total time: 1058.38s) ⏎ First error in model 'AGENCY_AD_ROW_VIDEO': Database Error in model AGENCY_AD_ROW_VIDEO (models/silver/agency/AGENCY_AD_ROW_VIDEO.sql) ⏎   000904 (42000): SQL compilation error: error line 42 at position 8 ⏎   invalid identifier 'UPPER_CMPGN_NM' ⏎ Error 2 in model 'AGENCY_AD_ROW_REBRDC': Database Error in model AGENCY_AD_ROW_REBRDC (models/silver/agency/AGENCY_AD_ROW_REBRDC.sql) ⏎   000904 (42000): SQL compilation error: error line 41 at position 8 ⏎   invalid identifier 'CMPGN_CD'.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c7f94d-0002-3e97-0001-72de0816f7b6') for more details.</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01c7fc46-0002-410b-0001-72de08309a62</t>
+          <t>01c80a21-0002-42f2-0001-72de08de9716</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-26 18:42:39.203000+09:00</t>
+          <t>2026-10-29 05:49:01.720000+09:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-26 18:42:58.436000+09:00</t>
+          <t>2026-10-29 05:49:18.296000+09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1072,17 +1044,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01c7fc47-0002-410b-0001-72de08309c4a</t>
+          <t>01c80a21-0002-42f2-0001-72de08de994a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-26 18:43:05.592000+09:00</t>
+          <t>2026-10-29 05:49:19.094000+09:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-26 18:43:29.166000+09:00</t>
+          <t>2026-10-29 05:49:41.853000+09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1101,17 +1073,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01c7fc47-0002-410b-0001-72de08309e5a</t>
+          <t>01c80a21-0002-44fa-0001-72de08dea072</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-26 18:43:30.489000+09:00</t>
+          <t>2026-10-29 05:49:42.520000+09:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-26 18:43:48.890000+09:00</t>
+          <t>2026-10-29 05:49:59.969000+09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1122,25 +1094,29 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 seed(s) failed out of 6 total (total time: 3.61s) ⏎ First error in seed 'MAP_AT_GA_LINK': Database Error in seed MAP_AT_GA_LINK (seeds/MAP_AT_GA_LINK.csv) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on schema 'SILVER'. Your primary role GN_DW_DBT must have CREATE TABLE granted on SCHEMA GN_DW.SILVER..  ⏎ Context: DBT 1.9.4, Command: dbt seed. ⏎  Run select system$get_dbt_log('01c80a21-0002-44fa-0001-72de08dea072') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01c7fc47-0002-410b-0001-72de0830c0f2</t>
+          <t>01c80a22-0002-42f2-0001-72de08deb186</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-26 18:43:49.918000+09:00</t>
+          <t>2026-10-29 05:50:13.997000+09:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-26 18:57:47.586000+09:00</t>
+          <t>2026-10-29 05:50:48.816000+09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1148,40 +1124,44 @@
           <t>build</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>--select CRM_SEND_REQUEST+</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 72 total (total time: 20.09s) ⏎ First error in model 'FACT_AT_GA_LINK_MAP': Database Error in model FACT_AT_GA_LINK_MAP (models/gold/fact/FACT_AT_GA_LINK_MAP.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on schema 'GOLD'. Your primary role GN_DW_DBT must have CREATE TABLE granted on SCHEMA GN_DW.GOLD. ⏎   compiled code at /tmp/dbt_output/target/run/gn_dw_silver/models/gold/fact/FACT_AT_GA_LINK_MAP.sql.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c80a22-0002-42f2-0001-72de08deb186') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01c7fc55-0002-410b-0001-72de083198b6</t>
+          <t>01c80a23-0002-42f2-0001-72de08debef2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-26 18:57:54.107000+09:00</t>
+          <t>2026-10-29 05:51:55.883000+09:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-26 20:05:43.892000+09:00</t>
+          <t>2026-10-29 05:52:25.041000+09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--select BIGQUERY_BASIC+ BIGQUERY_SESSION+ FACT_MESSAGE_DISPATCH+ FACT_BIGQUERY_SESSION+ --vars '{"bigquery_dt_ranges": </t>
-        </is>
-      </c>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -1192,22 +1172,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01c7feed-0002-41a1-0001-72de084be766</t>
+          <t>01c80a24-0002-42f2-0001-72de08ded32a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 06:01:00.848000+09:00</t>
+          <t>2026-10-29 05:52:34.553000+09:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-27 06:23:04.031000+09:00</t>
+          <t>2026-10-29 05:52:54.311000+09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1221,51 +1201,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01c80020-0002-41a1-0001-72de085a6e12</t>
+          <t>01c80a25-0002-42f2-0001-72de08ded75e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 11:08:49.908000+09:00</t>
+          <t>2026-10-29 05:53:00.344000+09:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-27 11:09:13.146000+09:00</t>
+          <t>2026-10-29 05:53:34.627000+09:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>parse</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>--select CRM_SEND_REQUEST+</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 72 total (total time: 19.83s) ⏎ First error in model 'FACT_AT_GA_LINK_MAP': Database Error in model FACT_AT_GA_LINK_MAP (models/gold/fact/FACT_AT_GA_LINK_MAP.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on schema 'GOLD'. Your primary role GN_DW_DBT must have CREATE TABLE granted on SCHEMA GN_DW.GOLD. ⏎   compiled code at /tmp/dbt_output/target/run/gn_dw_silver/models/gold/fact/FACT_AT_GA_LINK_MAP.sql.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c80a25-0002-42f2-0001-72de08ded75e') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01c80021-0002-41fc-0001-72de085a991e</t>
+          <t>01c80a26-0002-42f2-0001-72de08dee47e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 11:09:14.090000+09:00</t>
+          <t>2026-10-29 05:54:21.636000+09:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-27 11:09:39.225000+09:00</t>
+          <t>2026-10-29 05:54:41.576000+09:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>compile</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1279,60 +1267,1022 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01c80021-0002-41fc-0001-72de085a9d5a</t>
+          <t>01c80a26-0002-44fa-0001-72de08def162</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 11:09:48.849000+09:00</t>
+          <t>2026-10-29 05:54:42.198000+09:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-27 11:10:07.891000+09:00</t>
+          <t>2026-10-29 05:56:38.568000+09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>--select CRM_SEND_REQUEST+</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 72 total (total time: 101.84s) ⏎ First error in model 'FACT_MESSAGE_DISPATCH': Database Error in model FACT_MESSAGE_DISPATCH (models/gold/fact/FACT_MESSAGE_DISPATCH.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'FACT_MESSAGE_DISPATCH'..  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c80a26-0002-44fa-0001-72de08def162') for more details.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01c80022-0002-41fc-0001-72de085ad02e</t>
+          <t>01c80a2b-0002-44fa-0001-72de08df32ca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 11:10:08.883000+09:00</t>
+          <t>2026-10-29 05:59:20.249000+09:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:46.976000+09:00</t>
+          <t>2026-10-29 06:06:08.386000+09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>--select CRM_SEND_REQUEST+</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>01c80a2d-0002-44d1-0001-72de08c96e8e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:01:00.435000+09:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:22:22.676000+09:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 800 total (total time: 1250.46s) ⏎ First error in model 'FACT_AD_PERFORMANCE': Database Error in model FACT_AD_PERFORMANCE (models/gold/fact/FACT_AD_PERFORMANCE.sql) ⏎   003001 (42501): SQL access control error: ⏎   Insufficient privileges to operate on table 'FACT_AD_PERFORMANCE'..  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c80a2d-0002-44d1-0001-72de08c96e8e') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>01c80a46-0002-44fa-0001-72de08e0e64e</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:26:13.512000+09:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:31:08.212000+09:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>--select CRM_SEND_REQUEST+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>01c80a50-0002-4527-0001-72de08e183fe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:36:07.952000+09:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:36:24.398000+09:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>01c80a50-0002-4396-0001-72de08e17852</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:36:24.983000+09:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:36:49.136000+09:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>01c80a50-0002-42f2-0001-72de08e19602</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:36:58.237000+09:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:37:17.724000+09:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>01c80a51-0002-42f2-0001-72de08e19a66</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:37:24.927000+09:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:42:06.917000+09:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>--select MAP_AT_GA_LINK+</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>01c80a5b-0002-4396-0001-72de08e29262</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:47:29.339000+09:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:48:12.670000+09:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>--select FACT_AD_PERFORMANCE+ FACT_MKTG_CAMPAIGN_MONTHLY_COST</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>01c80a74-0002-454b-0001-72de08e4e1ea</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:12:56.291000+09:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:13:16.253000+09:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>01c80a75-0002-4396-0001-72de08e4f7ae</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:13:16.866000+09:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:13:40.610000+09:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>01c80a75-0002-4396-0001-72de08e4f8fa</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:13:41.857000+09:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:14:03.001000+09:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>01c80a76-0002-42f2-0001-72de08e5147e</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:14:03.579000+09:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:33:55.995000+09:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>01c80b7c-0002-44fa-0001-72de08f3a656</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:36:26.647000+09:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:38:28.834000+09:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>test</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>01c80c0e-0002-42f2-0001-72de08fb776e</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:02:59.788000+09:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:20:21.307000+09:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 150 total (total time: 1015.55s) ⏎ First error in model 'ERP_BUDGET_YEARLY': Database Error in model ERP_BUDGET_YEARLY (models/silver/erp/ERP_BUDGET_YEARLY.sql) ⏎   100072: DML operation to table GN_DW.SILVER.ERP_BUDGET_YEARLY failed on column BUDGET_YEAR with error: NULL result in a non-nullable column ⏎   compiled code at /tmp/dbt_output/target/run/gn_dw_silver/models/silver/erp/ERP_BUDGET_YEARLY.sql.  ⏎ Context: DBT 1.9.4, Command: dbt run. ⏎  Run select system$get_dbt_log('01c80c0e-0002-42f2-0001-72de08fb776e') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>01c80d18-0002-4396-0001-72de09096cea</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:28:16.321000+09:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:28:43.138000+09:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>01c80d18-0002-42f2-0001-72de0909a0be</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:28:51.098000+09:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:29:12.112000+09:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>--select ERP_BUDGET_YEARLY+</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DBT job failed: 1 model(s) failed out of 20 total (total time: 6.35s) ⏎ First error in model 'ERP_BUDGET_YEARLY': Database Error in model ERP_BUDGET_YEARLY (models/silver/erp/ERP_BUDGET_YEARLY.sql) ⏎   100072: DML operation to table GN_DW.SILVER.ERP_BUDGET_YEARLY failed on column BUDGET_YEAR with error: NULL result in a non-nullable column ⏎   compiled code at /tmp/dbt_output/target/run/gn_dw_silver/models/silver/erp/ERP_BUDGET_YEARLY.sql.  ⏎ Context: DBT 1.9.4, Command: dbt build. ⏎  Run select system$get_dbt_log('01c80d18-0002-42f2-0001-72de0909a0be') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>01c80d19-0002-454a-0001-72de090996ca</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:29:49.558000+09:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:30:00.789000+09:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>--select ERP_BUDGET_YEARLY+</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>01c80d1a-0002-454a-0001-72de0909974a</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:30:03.322000+09:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:30:26.895000+09:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>--select ERP_BUDGET_YEARLY+</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎ [0m09:30:25  Got 151 results, configured to warn if != 0 ⏎ [0m09:30:25   ⏎ [0m09:30:25    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_erp_budget_yearly_grain.sql ⏎ [0m09:30:25   ⏎ [0m09:30:25  [33mWarning in test warn_map_coverage_budget_procedure (tests/warn_map_coverage_budget_procedure.sql)[0m ⏎ [0m09:30:25  Got 5 results, configured to warn if != 0 ⏎ [0m09:30:25   ⏎ [0m09:30:25    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_map_coverage_budget_procedure.sql ⏎ [0m09:30:25   ⏎ [0m09:30:25  Done. PASS=16 WARN=2 ERROR=2 SKIP=0 TOTAL=20. ⏎  Run select system$get_dbt_log('01c80d1a-0002-454a-0001-72de0909974a') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>01c80d1a-0002-44fa-0001-72de09098d92</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:30:56.513000+09:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:31:17.269000+09:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>--select ERP_BUDGET_YEARLY+</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>01c80d1c-0002-44fa-0001-72de0909e282</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:32:31.600000+09:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:32:55.228000+09:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>--select ERP_BUDGET_YEARLY+</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DBT job failed. Last output lines: ⏎ [0m09:32:53  Got 151 results, configured to warn if != 0 ⏎ [0m09:32:53   ⏎ [0m09:32:53    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_erp_budget_yearly_grain.sql ⏎ [0m09:32:53   ⏎ [0m09:32:53  [33mWarning in test warn_map_coverage_budget_procedure (tests/warn_map_coverage_budget_procedure.sql)[0m ⏎ [0m09:32:53  Got 5 results, configured to warn if != 0 ⏎ [0m09:32:53   ⏎ [0m09:32:53    compiled code at /tmp/dbt_output/target/compiled/gn_dw_silver/tests/warn_map_coverage_budget_procedure.sql ⏎ [0m09:32:53   ⏎ [0m09:32:53  Done. PASS=14 WARN=2 ERROR=2 SKIP=0 TOTAL=18. ⏎  Run select system$get_dbt_log('01c80d1c-0002-44fa-0001-72de0909e282') for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>01c80d21-0002-4396-0001-72de090a2bfe</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:37:47.265000+09:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:37:49.981000+09:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>01c80d21-0002-44fa-0001-72de090a37aa</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:37:58.849000+09:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:38:01.546000+09:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SQL execution canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>01c80d27-0002-460f-0001-72de090a99e6</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:43:19.122000+09:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:00:48.545000+09:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>01c80d83-0002-454a-0001-72de090ebce2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:15:44.600000+09:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:18:41.666000+09:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>01c80fcd-0002-44fa-0001-72de0929843e</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:01:00.499000+09:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:20:56.769000+09:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>01c8113d-0002-46ff-0001-72de093b8cee</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:09:55.436000+09:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:10:07.215000+09:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>parse</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>01c8113e-0002-44fa-0001-72de093b9c12</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:10:08.171000+09:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:10:30.500000+09:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>compile</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>01c8113e-0002-472e-0001-72de093bb266</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:10:31.591000+09:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:10:49.605000+09:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>01c8113e-0002-46ff-0001-72de093b8ffe</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:10:49.935000+09:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:30:27.842000+09:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>HANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DBT job failed: 20 model(s) failed out of 800 total (total time: 1145.36s) ⏎ First error in model 'WIDE_SPNSR_CLS_AGGR': Database Error in model WIDE_SPNSR_CLS_AGGR (models/gold/wide/WIDE_SPNSR_CLS_AGGR.sql) ⏎   003509 (23001): SQL execution error: Not authorized in a managed access schema. Use the schema owner role or a role with the MANAGE GRANTS privilege. ⏎   compiled code at target/run/gn_dw_…[절단 4684자]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>01c81175-0002-4773-0001-72de093eaa22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:05:44.929000+09:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:05:45.740000+09:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>retry</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UNHANDLED_ERROR</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No active warehouse selected in the current session.  Select an active warehouse with the 'use warehouse' command. ⏎ </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>01c81175-0002-4732-0001-72de093eb97a</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:05:56.447000+09:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:06:31.908000+09:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>retry</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1351,7 +2301,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1708,7 +2658,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -1742,7 +2692,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-27 11:11:43.732000+09:00</t>
+          <t>2026-10-30 13:06:21.262000+09:00</t>
         </is>
       </c>
     </row>
@@ -1759,7 +2709,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-27 11:10:57.486000+09:00</t>
+          <t>2026-10-30 12:15:30.830000+09:00</t>
         </is>
       </c>
     </row>
@@ -1776,7 +2726,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-27 11:10:57.506000+09:00</t>
+          <t>2026-10-30 12:15:30.877000+09:00</t>
         </is>
       </c>
     </row>
@@ -1793,7 +2743,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-27 11:10:57.482000+09:00</t>
+          <t>2026-10-30 12:15:31.179000+09:00</t>
         </is>
       </c>
     </row>
@@ -1810,7 +2760,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-27 11:10:35.808000+09:00</t>
+          <t>2026-10-30 12:16:57.387000+09:00</t>
         </is>
       </c>
     </row>
@@ -1839,12 +2789,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:32.583000+09:00</t>
+          <t>2026-10-30 12:16:02.820000+09:00</t>
         </is>
       </c>
     </row>
@@ -1861,7 +2811,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:27.438000+09:00</t>
+          <t>2026-10-30 12:11:35.564000+09:00</t>
         </is>
       </c>
     </row>
@@ -1878,7 +2828,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:27.923000+09:00</t>
+          <t>2026-10-30 12:11:35.541000+09:00</t>
         </is>
       </c>
     </row>
@@ -1895,7 +2845,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:32.031000+09:00</t>
+          <t>2026-10-30 12:26:22.467000+09:00</t>
         </is>
       </c>
     </row>
@@ -1912,7 +2862,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:32.663000+09:00</t>
+          <t>2026-10-30 12:20:24.997000+09:00</t>
         </is>
       </c>
     </row>
@@ -1929,7 +2879,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:37.655000+09:00</t>
+          <t>2026-10-30 13:06:27.882000+09:00</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2896,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-27 11:12:33.769000+09:00</t>
+          <t>2026-10-30 12:11:36.043000+09:00</t>
         </is>
       </c>
     </row>
@@ -1967,7 +2917,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2196,7 +3146,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2240,12 +3190,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>46781058299.0</t>
+          <t>46812370899.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-500833790007.0</t>
+          <t>-500802477407.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2267,12 +3217,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>60226852367.0</t>
+          <t>61450721152.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-236818228536.0</t>
+          <t>-235594359751.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2294,12 +3244,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>128.741962</t>
+          <t>131.27026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>74.498531</t>
+          <t>77.026829</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2321,12 +3271,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1584428.0</t>
+          <t>1540334.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1495.0</t>
+          <t>-45589.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2348,12 +3298,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>935034.0</t>
+          <t>888141.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31970.0</t>
+          <t>-14923.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2375,12 +3325,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>947093601916.0</t>
+          <t>947204371692.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51915292808.0</t>
+          <t>52026062584.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2402,12 +3352,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>961981566649.0</t>
+          <t>962009296649.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>70021775761.0</t>
+          <t>70049505761.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2429,12 +3379,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>85.767719</t>
+          <t>85.767725</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0005660000000062837</t>
+          <t>0.000572000000005346</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2564,12 +3514,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4067856.2614</t>
+          <t>3948249.731</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1775978.2614000002</t>
+          <t>1656371.7310000001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2591,12 +3541,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1078353.0</t>
+          <t>1028572.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40091.0</t>
+          <t>-9690.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2618,12 +3568,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1009981.0</t>
+          <t>1014772.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-124145.0</t>
+          <t>-119354.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2645,12 +3595,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>320845.0</t>
+          <t>321069.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-86378.0</t>
+          <t>-86154.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2672,12 +3622,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>219935.0</t>
+          <t>219923.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-26693.0</t>
+          <t>-26705.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2699,12 +3649,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>44646949.0</t>
+          <t>44777483.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6176169.0</t>
+          <t>6306703.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2726,12 +3676,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1067787.0</t>
+          <t>1069626.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>35816.0</t>
+          <t>37655.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2753,12 +3703,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16553140.0</t>
+          <t>16553094.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-10297.0</t>
+          <t>-10343.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2784,7 +3734,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -2893,22 +3843,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>792</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22554689599.00</t>
+          <t>22586002199.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15161016993.00</t>
+          <t>16384885778.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>72.54</t>
         </is>
       </c>
     </row>
@@ -2929,7 +3879,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n05_report_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = _ENV/ZL50263/N05_*.csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
